--- a/results/PRISM/prism_hsp90_inhibitors.xlsx
+++ b/results/PRISM/prism_hsp90_inhibitors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>DRUG</t>
   </si>
@@ -40,9 +40,6 @@
     <t>FDR</t>
   </si>
   <si>
-    <t>TRANSLATIONALLY_PRIOROTISED</t>
-  </si>
-  <si>
     <t>ALVESPIMYCIN</t>
   </si>
   <si>
@@ -61,12 +58,18 @@
     <t>GANETESPIB</t>
   </si>
   <si>
+    <t>4-CHLOROPHENYLGUANIDINE</t>
+  </si>
+  <si>
     <t>NMS-E973</t>
   </si>
   <si>
     <t>TANESPIMYCIN</t>
   </si>
   <si>
+    <t>SNX 2112</t>
+  </si>
+  <si>
     <t>SNX-5422</t>
   </si>
   <si>
@@ -76,6 +79,9 @@
     <t>PU-H71</t>
   </si>
   <si>
+    <t>GUANIDINE</t>
+  </si>
+  <si>
     <t>BRD-K83988098-001-02-0</t>
   </si>
   <si>
@@ -94,12 +100,18 @@
     <t>BRD-K38852836-001-02-1</t>
   </si>
   <si>
+    <t>BRD-K39160765-003-02-9</t>
+  </si>
+  <si>
     <t>BRD-K58770988-001-01-8</t>
   </si>
   <si>
     <t>BRD-K81473043-001-19-5</t>
   </si>
   <si>
+    <t>BRD-K71281111-001-04-3</t>
+  </si>
+  <si>
     <t>BRD-K73197500-001-02-2</t>
   </si>
   <si>
@@ -109,6 +121,9 @@
     <t>BRD-K36529613-001-02-6</t>
   </si>
   <si>
+    <t>BRD-K76037122-001-02-5</t>
+  </si>
+  <si>
     <t>HSP90AA1</t>
   </si>
   <si>
@@ -116,6 +131,9 @@
   </si>
   <si>
     <t>HSP90AA1 | WT1</t>
+  </si>
+  <si>
+    <t>ALDH2 | DLG4 | GAMT | RNASE1</t>
   </si>
   <si>
     <t>CHEK1 | HSP90AA1</t>
@@ -456,10 +474,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -484,22 +502,19 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E2">
         <v>43</v>
@@ -513,22 +528,19 @@
       <c r="H2">
         <v>0.02376920804593734</v>
       </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E3">
         <v>43</v>
@@ -542,19 +554,16 @@
       <c r="H3">
         <v>0.1316654378412472</v>
       </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>30</v>
@@ -568,19 +577,16 @@
       <c r="H4">
         <v>0.6996036362344265</v>
       </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E5">
         <v>28</v>
@@ -594,22 +600,19 @@
       <c r="H5">
         <v>0.9977577719518268</v>
       </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E6">
         <v>42</v>
@@ -623,22 +626,19 @@
       <c r="H6">
         <v>0.9977577719518268</v>
       </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E7">
         <v>43</v>
@@ -652,150 +652,207 @@
       <c r="H7">
         <v>0.9977577719518268</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8">
+        <v>29</v>
+      </c>
+      <c r="F8">
+        <v>-0.255099989997961</v>
+      </c>
+      <c r="G8">
+        <v>0.1816966511721846</v>
+      </c>
+      <c r="H8">
+        <v>0.9977577719518268</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8">
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9">
         <v>30</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>-0.2369299221357063</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>0.2074464796327853</v>
       </c>
-      <c r="H8">
-        <v>0.9977577719518268</v>
-      </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
+      <c r="H9">
+        <v>0.9977577719518268</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9">
-        <v>42</v>
-      </c>
-      <c r="F9">
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10">
+        <v>42</v>
+      </c>
+      <c r="F10">
         <v>-0.1919695313759173</v>
       </c>
-      <c r="G9">
+      <c r="G10">
         <v>0.2232521391592944</v>
       </c>
-      <c r="H9">
-        <v>0.9977577719518268</v>
-      </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
+      <c r="H10">
+        <v>0.9977577719518268</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10">
-        <v>26</v>
-      </c>
-      <c r="F10">
-        <v>-0.03794871794871794</v>
-      </c>
-      <c r="G10">
-        <v>0.8539737921729723</v>
-      </c>
-      <c r="H10">
-        <v>0.9977577719518268</v>
-      </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
       <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>30</v>
       </c>
       <c r="F11">
+        <v>-0.1203559510567297</v>
+      </c>
+      <c r="G11">
+        <v>0.5263973902969712</v>
+      </c>
+      <c r="H11">
+        <v>0.9977577719518268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12">
+        <v>26</v>
+      </c>
+      <c r="F12">
+        <v>-0.03794871794871794</v>
+      </c>
+      <c r="G12">
+        <v>0.8539737921729723</v>
+      </c>
+      <c r="H12">
+        <v>0.9977577719518268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13">
         <v>-0.0135706340378198</v>
       </c>
-      <c r="G11">
+      <c r="G13">
         <v>0.943259139365723</v>
       </c>
-      <c r="H11">
-        <v>0.9977577719518268</v>
-      </c>
-      <c r="I11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="H13">
+        <v>0.9977577719518268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14">
         <v>30</v>
       </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12">
-        <v>30</v>
-      </c>
-      <c r="F12">
+      <c r="F14">
         <v>0.07274749721913237</v>
       </c>
-      <c r="G12">
+      <c r="G14">
         <v>0.7024388474244606</v>
       </c>
-      <c r="H12">
-        <v>0.9977577719518268</v>
-      </c>
-      <c r="I12" t="b">
-        <v>0</v>
+      <c r="H14">
+        <v>0.9977577719518268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15">
+        <v>26</v>
+      </c>
+      <c r="F15">
+        <v>0.1279814513014585</v>
+      </c>
+      <c r="G15">
+        <v>0.5332477809316704</v>
+      </c>
+      <c r="H15">
+        <v>0.9977577719518268</v>
       </c>
     </row>
   </sheetData>

--- a/results/PRISM/prism_hsp90_inhibitors.xlsx
+++ b/results/PRISM/prism_hsp90_inhibitors.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
   <si>
     <t>DRUG</t>
   </si>
@@ -58,9 +58,6 @@
     <t>GANETESPIB</t>
   </si>
   <si>
-    <t>4-CHLOROPHENYLGUANIDINE</t>
-  </si>
-  <si>
     <t>NMS-E973</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t>PU-H71</t>
   </si>
   <si>
-    <t>GUANIDINE</t>
-  </si>
-  <si>
     <t>BRD-K83988098-001-02-0</t>
   </si>
   <si>
@@ -100,9 +94,6 @@
     <t>BRD-K38852836-001-02-1</t>
   </si>
   <si>
-    <t>BRD-K39160765-003-02-9</t>
-  </si>
-  <si>
     <t>BRD-K58770988-001-01-8</t>
   </si>
   <si>
@@ -121,9 +112,6 @@
     <t>BRD-K36529613-001-02-6</t>
   </si>
   <si>
-    <t>BRD-K76037122-001-02-5</t>
-  </si>
-  <si>
     <t>HSP90AA1</t>
   </si>
   <si>
@@ -131,9 +119,6 @@
   </si>
   <si>
     <t>HSP90AA1 | WT1</t>
-  </si>
-  <si>
-    <t>ALDH2 | DLG4 | GAMT | RNASE1</t>
   </si>
   <si>
     <t>CHEK1 | HSP90AA1</t>
@@ -474,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -508,13 +493,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <v>43</v>
@@ -534,13 +519,13 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E3">
         <v>43</v>
@@ -560,10 +545,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>30</v>
@@ -583,10 +568,10 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E5">
         <v>28</v>
@@ -606,13 +591,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E6">
         <v>42</v>
@@ -632,13 +617,13 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E7">
         <v>43</v>
@@ -658,22 +643,19 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>-0.255099989997961</v>
+        <v>-0.2369299221357063</v>
       </c>
       <c r="G8">
-        <v>0.1816966511721846</v>
+        <v>0.2074464796327853</v>
       </c>
       <c r="H8">
         <v>0.9977577719518268</v>
@@ -684,19 +666,22 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
       </c>
       <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9">
         <v>42</v>
       </c>
-      <c r="E9">
-        <v>30</v>
-      </c>
       <c r="F9">
-        <v>-0.2369299221357063</v>
+        <v>-0.1919695313759173</v>
       </c>
       <c r="G9">
-        <v>0.2074464796327853</v>
+        <v>0.2232521391592944</v>
       </c>
       <c r="H9">
         <v>0.9977577719518268</v>
@@ -707,22 +692,19 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10">
-        <v>42</v>
-      </c>
       <c r="F10">
-        <v>-0.1919695313759173</v>
+        <v>-0.1203559510567297</v>
       </c>
       <c r="G10">
-        <v>0.2232521391592944</v>
+        <v>0.5263973902969712</v>
       </c>
       <c r="H10">
         <v>0.9977577719518268</v>
@@ -733,19 +715,22 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>-0.1203559510567297</v>
+        <v>-0.03794871794871794</v>
       </c>
       <c r="G11">
-        <v>0.5263973902969712</v>
+        <v>0.8539737921729723</v>
       </c>
       <c r="H11">
         <v>0.9977577719518268</v>
@@ -756,22 +741,22 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E12">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F12">
-        <v>-0.03794871794871794</v>
+        <v>-0.0135706340378198</v>
       </c>
       <c r="G12">
-        <v>0.8539737921729723</v>
+        <v>0.943259139365723</v>
       </c>
       <c r="H12">
         <v>0.9977577719518268</v>
@@ -782,76 +767,24 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="E13">
         <v>30</v>
       </c>
       <c r="F13">
-        <v>-0.0135706340378198</v>
+        <v>0.07274749721913237</v>
       </c>
       <c r="G13">
-        <v>0.943259139365723</v>
+        <v>0.7024388474244606</v>
       </c>
       <c r="H13">
-        <v>0.9977577719518268</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14">
-        <v>30</v>
-      </c>
-      <c r="F14">
-        <v>0.07274749721913237</v>
-      </c>
-      <c r="G14">
-        <v>0.7024388474244606</v>
-      </c>
-      <c r="H14">
-        <v>0.9977577719518268</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15">
-        <v>26</v>
-      </c>
-      <c r="F15">
-        <v>0.1279814513014585</v>
-      </c>
-      <c r="G15">
-        <v>0.5332477809316704</v>
-      </c>
-      <c r="H15">
         <v>0.9977577719518268</v>
       </c>
     </row>
